--- a/cloudflare-deploy/public/library/teacher/teacher-en.xlsx
+++ b/cloudflare-deploy/public/library/teacher/teacher-en.xlsx
@@ -1205,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2218,6 +2218,33 @@
       <c r="E39" s="20" t="inlineStr">
         <is>
           <t>If you forget passwords often, register an app passkey — a glance gets you in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="54" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>🌟</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="inlineStr">
+        <is>
+          <t>Parent Monthly Report (built from your evaluations)</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>Fill in the lesson evaluation conscientiously, as usual. → Pronunciation practice and judgment-training records feed the axes automatically. → Review and refine the Teacher's Note AI draft on the report. → Preview to confirm the pentagon is well filled in.</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="inlineStr">
+        <is>
+          <t>Even a one-line evaluation each lesson makes the month-end report complete itself.</t>
         </is>
       </c>
     </row>
@@ -2235,7 +2262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F424"/>
+  <dimension ref="A1:F435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6941,10 +6968,131 @@
       <c r="E424" s="33" t="n"/>
       <c r="F424" s="33" t="n"/>
     </row>
+    <row r="426" ht="26" customHeight="1">
+      <c r="A426" s="21" t="inlineStr">
+        <is>
+          <t>37  🌟 Parent Monthly Report (built from your evaluations)  —  The five axes come from the evaluations you leave</t>
+        </is>
+      </c>
+      <c r="B426" s="22" t="n"/>
+      <c r="C426" s="22" t="n"/>
+      <c r="D426" s="22" t="n"/>
+      <c r="E426" s="22" t="n"/>
+      <c r="F426" s="22" t="n"/>
+    </row>
+    <row r="427" ht="42" customHeight="1">
+      <c r="A427" s="23" t="inlineStr">
+        <is>
+          <t>📖 The five axes of the pentagon monthly report parents receive (Pronunciation &amp; Fluency / Vocabulary / Sentence Building / Class Attitude / Participation) are filled from the lesson evaluations and pronunciation records you leave. The more consistently you evaluate, the more accurate and complete the report. The Teacher's Note is an AI draft you review and adjust before it goes out.</t>
+        </is>
+      </c>
+      <c r="B427" s="24" t="n"/>
+      <c r="C427" s="24" t="n"/>
+      <c r="D427" s="24" t="n"/>
+      <c r="E427" s="24" t="n"/>
+      <c r="F427" s="24" t="n"/>
+    </row>
+    <row r="428">
+      <c r="A428" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B428" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="429" ht="30" customHeight="1">
+      <c r="A429" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B429" s="28" t="inlineStr">
+        <is>
+          <t>Fill in the lesson evaluation conscientiously, as usual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="430" ht="30" customHeight="1">
+      <c r="A430" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B430" s="28" t="inlineStr">
+        <is>
+          <t>Pronunciation practice and judgment-training records feed the axes automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="431" ht="30" customHeight="1">
+      <c r="A431" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B431" s="28" t="inlineStr">
+        <is>
+          <t>Review and refine the Teacher's Note AI draft on the report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="432" ht="30" customHeight="1">
+      <c r="A432" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B432" s="28" t="inlineStr">
+        <is>
+          <t>Preview to confirm the pentagon is well filled in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="433" ht="24" customHeight="1">
+      <c r="A433" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B433" s="30" t="inlineStr">
+        <is>
+          <t>Only axes with values are filled — no evaluation means that axis looks empty.</t>
+        </is>
+      </c>
+      <c r="C433" s="31" t="n"/>
+      <c r="D433" s="31" t="n"/>
+      <c r="E433" s="31" t="n"/>
+      <c r="F433" s="31" t="n"/>
+    </row>
+    <row r="434" ht="24" customHeight="1">
+      <c r="A434" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B434" s="30" t="inlineStr">
+        <is>
+          <t>Consistent evaluations matter more than a long comment.</t>
+        </is>
+      </c>
+      <c r="C434" s="31" t="n"/>
+      <c r="D434" s="31" t="n"/>
+      <c r="E434" s="31" t="n"/>
+      <c r="F434" s="31" t="n"/>
+    </row>
+    <row r="435" ht="30" customHeight="1">
+      <c r="A435" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · Even a one-line evaluation each lesson makes the month-end report complete itself.</t>
+        </is>
+      </c>
+      <c r="B435" s="33" t="n"/>
+      <c r="C435" s="33" t="n"/>
+      <c r="D435" s="33" t="n"/>
+      <c r="E435" s="33" t="n"/>
+      <c r="F435" s="33" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="388">
+  <mergeCells count="398">
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B122:F122"/>
+    <mergeCell ref="B432:F432"/>
     <mergeCell ref="B276:F276"/>
     <mergeCell ref="B214:F214"/>
     <mergeCell ref="B18:F18"/>
@@ -6971,6 +7119,7 @@
     <mergeCell ref="B368:F368"/>
     <mergeCell ref="B135:F135"/>
     <mergeCell ref="B306:F306"/>
+    <mergeCell ref="B433:F433"/>
     <mergeCell ref="B233:F233"/>
     <mergeCell ref="B420:F420"/>
     <mergeCell ref="B224:F224"/>
@@ -6987,6 +7136,7 @@
     <mergeCell ref="B82:F82"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A199:F199"/>
+    <mergeCell ref="A435:F435"/>
     <mergeCell ref="B19:F19"/>
     <mergeCell ref="B146:F146"/>
     <mergeCell ref="B317:F317"/>
@@ -7100,6 +7250,7 @@
     <mergeCell ref="B226:F226"/>
     <mergeCell ref="A402:F402"/>
     <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B428:F428"/>
     <mergeCell ref="B284:F284"/>
     <mergeCell ref="B222:F222"/>
     <mergeCell ref="B344:F344"/>
@@ -7109,6 +7260,7 @@
     <mergeCell ref="B110:F110"/>
     <mergeCell ref="B286:F286"/>
     <mergeCell ref="A128:F128"/>
+    <mergeCell ref="A426:F426"/>
     <mergeCell ref="A364:F364"/>
     <mergeCell ref="A219:F219"/>
     <mergeCell ref="B297:F297"/>
@@ -7130,9 +7282,11 @@
     <mergeCell ref="B236:F236"/>
     <mergeCell ref="B307:F307"/>
     <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B429:F429"/>
     <mergeCell ref="B223:F223"/>
     <mergeCell ref="B294:F294"/>
     <mergeCell ref="B195:F195"/>
+    <mergeCell ref="B431:F431"/>
     <mergeCell ref="B60:F60"/>
     <mergeCell ref="B231:F231"/>
     <mergeCell ref="B287:F287"/>
@@ -7142,6 +7296,7 @@
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="B241:F241"/>
     <mergeCell ref="A260:F260"/>
+    <mergeCell ref="B434:F434"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B142:F142"/>
     <mergeCell ref="B80:F80"/>
@@ -7200,6 +7355,7 @@
     <mergeCell ref="A94:F94"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B334:F334"/>
+    <mergeCell ref="A427:F427"/>
     <mergeCell ref="B309:F309"/>
     <mergeCell ref="B113:F113"/>
     <mergeCell ref="B380:F380"/>
@@ -7318,6 +7474,7 @@
     <mergeCell ref="B67:F67"/>
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B430:F430"/>
     <mergeCell ref="B417:F417"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="B196:F196"/>
